--- a/UB-2.xlsx
+++ b/UB-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/twalha/Library/Mobile Documents/com~apple~CloudDocs/A-Uni/Year 3/Sem 2/G7 Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86D5AC4-AD71-144A-B57E-F0A4ADF2BE46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122F8836-EA22-A846-9653-3B0153184EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Steel Section Properties Data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Section Designation</t>
   </si>
@@ -50,18 +50,6 @@
     <t>rz​ (cm)</t>
   </si>
   <si>
-    <t>Zey​ (cm3)</t>
-  </si>
-  <si>
-    <t>Zez​ (cm3)</t>
-  </si>
-  <si>
-    <t>Zpy​ (cm3)</t>
-  </si>
-  <si>
-    <t>Zpz​ (cm3)</t>
-  </si>
-  <si>
     <t>U</t>
   </si>
   <si>
@@ -192,6 +180,27 @@
   </si>
   <si>
     <t>Area (mm2)</t>
+  </si>
+  <si>
+    <t>Web tw​ (mm)</t>
+  </si>
+  <si>
+    <t>Wyy​ (cm3)</t>
+  </si>
+  <si>
+    <t>Wzz (cm3)</t>
+  </si>
+  <si>
+    <t>Ezz​ (cm3)</t>
+  </si>
+  <si>
+    <t>Eyy (cm3)</t>
+  </si>
+  <si>
+    <t>Flange tf (mm)</t>
+  </si>
+  <si>
+    <t>Depth (h) mm</t>
   </si>
 </sst>
 </file>
@@ -454,10 +463,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,36 +483,45 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
+        <v>48</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1">
         <v>8250</v>
@@ -544,10 +562,19 @@
       <c r="N2" s="1">
         <v>4210</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O2">
+        <v>6</v>
+      </c>
+      <c r="P2">
+        <v>349</v>
+      </c>
+      <c r="Q2">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1">
         <v>12500</v>
@@ -588,10 +615,19 @@
       <c r="N3" s="1">
         <v>4970</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O3">
+        <v>6.4</v>
+      </c>
+      <c r="P3">
+        <v>398</v>
+      </c>
+      <c r="Q3">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1">
         <v>10200</v>
@@ -632,10 +668,19 @@
       <c r="N4" s="1">
         <v>4980</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O4">
+        <v>6.6</v>
+      </c>
+      <c r="P4">
+        <v>353.4</v>
+      </c>
+      <c r="Q4">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B5" s="1">
         <v>8500</v>
@@ -676,10 +721,19 @@
       <c r="N5" s="1">
         <v>5130</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O5">
+        <v>6</v>
+      </c>
+      <c r="P5">
+        <v>303.39999999999998</v>
+      </c>
+      <c r="Q5">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1">
         <v>12100</v>
@@ -720,10 +774,19 @@
       <c r="N6" s="1">
         <v>5730</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O6">
+        <v>7</v>
+      </c>
+      <c r="P6">
+        <v>351.4</v>
+      </c>
+      <c r="Q6">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B7" s="1">
         <v>15700</v>
@@ -764,10 +827,19 @@
       <c r="N7" s="1">
         <v>5860</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O7">
+        <v>6.8</v>
+      </c>
+      <c r="P7">
+        <v>403.2</v>
+      </c>
+      <c r="Q7">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B8" s="1">
         <v>9900</v>
@@ -808,10 +880,19 @@
       <c r="N8" s="1">
         <v>5870</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O8">
+        <v>6.7</v>
+      </c>
+      <c r="P8">
+        <v>306.60000000000002</v>
+      </c>
+      <c r="Q8">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B9" s="1">
         <v>14100</v>
@@ -852,10 +933,19 @@
       <c r="N9" s="1">
         <v>6490.0000000000009</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O9">
+        <v>7.4</v>
+      </c>
+      <c r="P9">
+        <v>355</v>
+      </c>
+      <c r="Q9">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1">
         <v>21400</v>
@@ -896,10 +986,19 @@
       <c r="N10" s="1">
         <v>6659.9999999999991</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O10">
+        <v>7.6</v>
+      </c>
+      <c r="P10">
+        <v>449.8</v>
+      </c>
+      <c r="Q10">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1">
         <v>18300</v>
@@ -940,10 +1039,19 @@
       <c r="N11" s="1">
         <v>6790.0000000000009</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O11">
+        <v>7.9</v>
+      </c>
+      <c r="P11">
+        <v>406.6</v>
+      </c>
+      <c r="Q11">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B12" s="1">
         <v>11700</v>
@@ -984,10 +1092,19 @@
       <c r="N12" s="1">
         <v>6880</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O12">
+        <v>7.9</v>
+      </c>
+      <c r="P12">
+        <v>310.39999999999998</v>
+      </c>
+      <c r="Q12">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1">
         <v>18700</v>
@@ -1028,10 +1145,19 @@
       <c r="N13" s="1">
         <v>6900</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O13">
+        <v>7.7</v>
+      </c>
+      <c r="P13">
+        <v>402.6</v>
+      </c>
+      <c r="Q13">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1">
         <v>16000</v>
@@ -1072,10 +1198,19 @@
       <c r="N14" s="1">
         <v>7259.9999999999991</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O14">
+        <v>8.1</v>
+      </c>
+      <c r="P14">
+        <v>358</v>
+      </c>
+      <c r="Q14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B15" s="1">
         <v>25500</v>
@@ -1116,10 +1251,19 @@
       <c r="N15" s="1">
         <v>7620</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O15">
+        <v>8.1</v>
+      </c>
+      <c r="P15">
+        <v>454.6</v>
+      </c>
+      <c r="Q15">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B16" s="1">
         <v>21600</v>
@@ -1160,10 +1304,19 @@
       <c r="N16" s="1">
         <v>7650</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O16">
+        <v>7.9</v>
+      </c>
+      <c r="P16">
+        <v>406.4</v>
+      </c>
+      <c r="Q16">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1">
         <v>35000</v>
@@ -1204,10 +1357,19 @@
       <c r="N17" s="1">
         <v>8370</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O17">
+        <v>8.9</v>
+      </c>
+      <c r="P17">
+        <v>524.70000000000005</v>
+      </c>
+      <c r="Q17">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1">
         <v>29400</v>
@@ -1248,10 +1410,19 @@
       <c r="N18" s="1">
         <v>8550</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O18">
+        <v>8.5</v>
+      </c>
+      <c r="P18">
+        <v>453.4</v>
+      </c>
+      <c r="Q18">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B19" s="1">
         <v>24300</v>
@@ -1292,10 +1463,19 @@
       <c r="N19" s="1">
         <v>8550</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O19">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="P19">
+        <v>409.4</v>
+      </c>
+      <c r="Q19">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B20" s="1">
         <v>19500</v>
@@ -1336,10 +1516,19 @@
       <c r="N20" s="1">
         <v>8550</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O20">
+        <v>9.1</v>
+      </c>
+      <c r="P20">
+        <v>363.4</v>
+      </c>
+      <c r="Q20">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1">
         <v>28900</v>
@@ -1380,10 +1569,19 @@
       <c r="N21" s="1">
         <v>8560</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O21">
+        <v>9</v>
+      </c>
+      <c r="P21">
+        <v>458</v>
+      </c>
+      <c r="Q21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B22" s="1">
         <v>32700</v>
@@ -1424,10 +1622,19 @@
       <c r="N22" s="1">
         <v>9450</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O22">
+        <v>9.6</v>
+      </c>
+      <c r="P22">
+        <v>462</v>
+      </c>
+      <c r="Q22">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1">
         <v>27300</v>
@@ -1468,10 +1675,19 @@
       <c r="N23" s="1">
         <v>9450</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O23">
+        <v>9.5</v>
+      </c>
+      <c r="P23">
+        <v>412.8</v>
+      </c>
+      <c r="Q23">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B24" s="1">
         <v>33300</v>
@@ -1512,10 +1728,19 @@
       <c r="N24" s="1">
         <v>9460</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O24">
+        <v>9</v>
+      </c>
+      <c r="P24">
+        <v>457</v>
+      </c>
+      <c r="Q24">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B25" s="1">
         <v>41100</v>
@@ -1556,10 +1781,19 @@
       <c r="N25" s="1">
         <v>9520</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O25">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="P25">
+        <v>529.1</v>
+      </c>
+      <c r="Q25">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B26" s="1">
         <v>37100</v>
@@ -1600,10 +1834,19 @@
       <c r="N26" s="1">
         <v>10400</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O26">
+        <v>9.9</v>
+      </c>
+      <c r="P26">
+        <v>460</v>
+      </c>
+      <c r="Q26">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B27" s="1">
         <v>47500</v>
@@ -1644,10 +1887,19 @@
       <c r="N27" s="1">
         <v>10500</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O27">
+        <v>9.6</v>
+      </c>
+      <c r="P27">
+        <v>528.29999999999995</v>
+      </c>
+      <c r="Q27">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B28" s="1">
         <v>36600</v>
@@ -1688,10 +1940,19 @@
       <c r="N28" s="1">
         <v>10500</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O28">
+        <v>10.5</v>
+      </c>
+      <c r="P28">
+        <v>465.8</v>
+      </c>
+      <c r="Q28">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B29" s="1">
         <v>48500</v>
@@ -1732,10 +1993,19 @@
       <c r="N29" s="1">
         <v>10800</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O29">
+        <v>10.3</v>
+      </c>
+      <c r="P29">
+        <v>534.9</v>
+      </c>
+      <c r="Q29">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B30" s="1">
         <v>31700</v>
@@ -1776,10 +2046,19 @@
       <c r="N30" s="1">
         <v>10900</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O30">
+        <v>10.9</v>
+      </c>
+      <c r="P30">
+        <v>417.2</v>
+      </c>
+      <c r="Q30">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B31" s="1">
         <v>41000</v>
@@ -1820,10 +2099,19 @@
       <c r="N31" s="1">
         <v>11400</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O31">
+        <v>10.5</v>
+      </c>
+      <c r="P31">
+        <v>463.4</v>
+      </c>
+      <c r="Q31">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B32" s="1">
         <v>55200</v>
@@ -1864,10 +2152,19 @@
       <c r="N32" s="1">
         <v>11700</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O32">
+        <v>10.1</v>
+      </c>
+      <c r="P32">
+        <v>533.1</v>
+      </c>
+      <c r="Q32">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B33" s="1">
         <v>45700</v>
@@ -1908,10 +2205,19 @@
       <c r="N33" s="1">
         <v>12500</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O33">
+        <v>11.4</v>
+      </c>
+      <c r="P33">
+        <v>467.2</v>
+      </c>
+      <c r="Q33">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B34" s="1">
         <v>61500</v>
@@ -1952,10 +2258,19 @@
       <c r="N34" s="1">
         <v>12900</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O34">
+        <v>10.8</v>
+      </c>
+      <c r="P34">
+        <v>536.70000000000005</v>
+      </c>
+      <c r="Q34">
+        <v>17.399999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B35" s="1">
         <v>48900</v>
@@ -1996,10 +2311,19 @@
       <c r="N35" s="1">
         <v>13500</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O35">
+        <v>12.6</v>
+      </c>
+      <c r="P35">
+        <v>469.2</v>
+      </c>
+      <c r="Q35">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B36" s="1">
         <v>66800</v>
@@ -2040,10 +2364,19 @@
       <c r="N36" s="1">
         <v>13900</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O36">
+        <v>11.6</v>
+      </c>
+      <c r="P36">
+        <v>539.5</v>
+      </c>
+      <c r="Q36">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B37" s="1">
         <v>76000</v>
@@ -2084,10 +2417,19 @@
       <c r="N37" s="1">
         <v>15500</v>
       </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O37">
+        <v>12.7</v>
+      </c>
+      <c r="P37">
+        <v>544.5</v>
+      </c>
+      <c r="Q37">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B38" s="1">
         <v>63800</v>
@@ -2128,10 +2470,19 @@
       <c r="N38" s="1">
         <v>17000</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O38">
+        <v>15.3</v>
+      </c>
+      <c r="P38">
+        <v>480.6</v>
+      </c>
+      <c r="Q38">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B39" s="1">
         <v>86100</v>
@@ -2172,10 +2523,19 @@
       <c r="N39" s="1">
         <v>17600</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="O39">
+        <v>14.7</v>
+      </c>
+      <c r="P39">
+        <v>549.1</v>
+      </c>
+      <c r="Q39">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B40" s="1">
         <v>79800</v>
@@ -2215,6 +2575,15 @@
       </c>
       <c r="N40" s="1">
         <v>20600</v>
+      </c>
+      <c r="O40">
+        <v>18</v>
+      </c>
+      <c r="P40">
+        <v>492</v>
+      </c>
+      <c r="Q40">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/UB-2.xlsx
+++ b/UB-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/twalha/Documents/GitHub/g6-analysis-tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8251FB66-5E9D-544D-AF60-CAFD9DD95DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E03722-B37D-5A4C-9A81-A6F032BD8E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Steel Section Properties Data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t>Section Designation</t>
   </si>
@@ -132,6 +132,123 @@
   </si>
   <si>
     <t>Root radius mm</t>
+  </si>
+  <si>
+    <t>356x127x33</t>
+  </si>
+  <si>
+    <t>406x140x39</t>
+  </si>
+  <si>
+    <t>356x127x39</t>
+  </si>
+  <si>
+    <t>305x165x40</t>
+  </si>
+  <si>
+    <t>356x171x45</t>
+  </si>
+  <si>
+    <t>406x140x46</t>
+  </si>
+  <si>
+    <t>305x165x46</t>
+  </si>
+  <si>
+    <t>356x171x51</t>
+  </si>
+  <si>
+    <t>457x152x52</t>
+  </si>
+  <si>
+    <t>406x140x53 +</t>
+  </si>
+  <si>
+    <t>305x165x54</t>
+  </si>
+  <si>
+    <t>406x178x54</t>
+  </si>
+  <si>
+    <t>356x171x57</t>
+  </si>
+  <si>
+    <t>457x152x60</t>
+  </si>
+  <si>
+    <t>406x178x60</t>
+  </si>
+  <si>
+    <t>533x165x66 +</t>
+  </si>
+  <si>
+    <t>457x191x67</t>
+  </si>
+  <si>
+    <t>406x178x67</t>
+  </si>
+  <si>
+    <t>356x171x67</t>
+  </si>
+  <si>
+    <t>457x152x67</t>
+  </si>
+  <si>
+    <t>457x152x74</t>
+  </si>
+  <si>
+    <t>406x178x74</t>
+  </si>
+  <si>
+    <t>457x191x74</t>
+  </si>
+  <si>
+    <t>533x165x75 +</t>
+  </si>
+  <si>
+    <t>457x191x82</t>
+  </si>
+  <si>
+    <t>533x210x82</t>
+  </si>
+  <si>
+    <t>457x152x82</t>
+  </si>
+  <si>
+    <t>533x165x85 +</t>
+  </si>
+  <si>
+    <t>406x178x85 +</t>
+  </si>
+  <si>
+    <t>457x191x89</t>
+  </si>
+  <si>
+    <t>533x210x92</t>
+  </si>
+  <si>
+    <t>457x191x98</t>
+  </si>
+  <si>
+    <t>533x210x101</t>
+  </si>
+  <si>
+    <t>457x191x106 +</t>
+  </si>
+  <si>
+    <t>533x210x109</t>
+  </si>
+  <si>
+    <t>533x210x122</t>
+  </si>
+  <si>
+    <t>457x191x133 +</t>
+  </si>
+  <si>
+    <t>533x210x138 +</t>
+  </si>
+  <si>
+    <t>457x191x161 +</t>
   </si>
 </sst>
 </file>
@@ -402,10 +519,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -461,7 +578,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -505,7 +622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -549,7 +666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -593,7 +710,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
@@ -637,7 +754,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -681,7 +798,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -725,7 +842,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -769,7 +886,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -813,7 +930,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
@@ -857,7 +974,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -901,7 +1018,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>27</v>
       </c>
@@ -945,7 +1062,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
@@ -989,7 +1106,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
@@ -1033,7 +1150,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>30</v>
       </c>
@@ -1077,7 +1194,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:18" ht="13" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>31</v>
       </c>
@@ -1119,6 +1236,2073 @@
       </c>
       <c r="R16" s="2">
         <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="1">
+        <v>8250</v>
+      </c>
+      <c r="C17" s="1">
+        <v>280</v>
+      </c>
+      <c r="D17" s="1">
+        <v>14</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2.58</v>
+      </c>
+      <c r="F17" s="1">
+        <v>473</v>
+      </c>
+      <c r="G17" s="1">
+        <v>44.7</v>
+      </c>
+      <c r="H17" s="1">
+        <v>543</v>
+      </c>
+      <c r="I17" s="1">
+        <v>70.2</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="K17" s="1">
+        <v>42.1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="M17" s="1">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="N17" s="1">
+        <v>4210</v>
+      </c>
+      <c r="O17">
+        <v>6</v>
+      </c>
+      <c r="P17">
+        <v>349</v>
+      </c>
+      <c r="Q17">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="1">
+        <v>12500</v>
+      </c>
+      <c r="C18" s="1">
+        <v>410</v>
+      </c>
+      <c r="D18" s="1">
+        <v>15.9</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2.87</v>
+      </c>
+      <c r="F18" s="1">
+        <v>629</v>
+      </c>
+      <c r="G18" s="1">
+        <v>57.8</v>
+      </c>
+      <c r="H18" s="1">
+        <v>724</v>
+      </c>
+      <c r="I18" s="1">
+        <v>90.8</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0.85799999999999998</v>
+      </c>
+      <c r="K18" s="1">
+        <v>47.4</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0.155</v>
+      </c>
+      <c r="M18" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="N18" s="1">
+        <v>4970</v>
+      </c>
+      <c r="O18">
+        <v>6.4</v>
+      </c>
+      <c r="P18">
+        <v>398</v>
+      </c>
+      <c r="Q18">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="1">
+        <v>10200</v>
+      </c>
+      <c r="C19" s="1">
+        <v>358</v>
+      </c>
+      <c r="D19" s="1">
+        <v>14.3</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2.68</v>
+      </c>
+      <c r="F19" s="1">
+        <v>576</v>
+      </c>
+      <c r="G19" s="1">
+        <v>56.8</v>
+      </c>
+      <c r="H19" s="1">
+        <v>659</v>
+      </c>
+      <c r="I19" s="1">
+        <v>89</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="K19" s="1">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0.105</v>
+      </c>
+      <c r="M19" s="1">
+        <v>15.1</v>
+      </c>
+      <c r="N19" s="1">
+        <v>4980</v>
+      </c>
+      <c r="O19">
+        <v>6.6</v>
+      </c>
+      <c r="P19">
+        <v>353.4</v>
+      </c>
+      <c r="Q19">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="1">
+        <v>8500</v>
+      </c>
+      <c r="C20" s="1">
+        <v>764</v>
+      </c>
+      <c r="D20" s="1">
+        <v>12.9</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3.86</v>
+      </c>
+      <c r="F20" s="1">
+        <v>560</v>
+      </c>
+      <c r="G20" s="1">
+        <v>92.6</v>
+      </c>
+      <c r="H20" s="1">
+        <v>623</v>
+      </c>
+      <c r="I20" s="1">
+        <v>142</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="K20" s="1">
+        <v>31</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="M20" s="1">
+        <v>14.7</v>
+      </c>
+      <c r="N20" s="1">
+        <v>5130</v>
+      </c>
+      <c r="O20">
+        <v>6</v>
+      </c>
+      <c r="P20">
+        <v>303.39999999999998</v>
+      </c>
+      <c r="Q20">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="1">
+        <v>12100</v>
+      </c>
+      <c r="C21" s="1">
+        <v>811</v>
+      </c>
+      <c r="D21" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="E21" s="1">
+        <v>3.76</v>
+      </c>
+      <c r="F21" s="1">
+        <v>687</v>
+      </c>
+      <c r="G21" s="1">
+        <v>94.8</v>
+      </c>
+      <c r="H21" s="1">
+        <v>775</v>
+      </c>
+      <c r="I21" s="1">
+        <v>147</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0.874</v>
+      </c>
+      <c r="K21" s="1">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0.23699999999999999</v>
+      </c>
+      <c r="M21" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="N21" s="1">
+        <v>5730</v>
+      </c>
+      <c r="O21">
+        <v>7</v>
+      </c>
+      <c r="P21">
+        <v>351.4</v>
+      </c>
+      <c r="Q21">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="1">
+        <v>15700</v>
+      </c>
+      <c r="C22" s="1">
+        <v>538</v>
+      </c>
+      <c r="D22" s="1">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E22" s="1">
+        <v>3.03</v>
+      </c>
+      <c r="F22" s="1">
+        <v>778</v>
+      </c>
+      <c r="G22" s="1">
+        <v>75.7</v>
+      </c>
+      <c r="H22" s="1">
+        <v>888</v>
+      </c>
+      <c r="I22" s="1">
+        <v>118</v>
+      </c>
+      <c r="J22" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="K22" s="1">
+        <v>39</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="M22" s="1">
+        <v>19</v>
+      </c>
+      <c r="N22" s="1">
+        <v>5860</v>
+      </c>
+      <c r="O22">
+        <v>6.8</v>
+      </c>
+      <c r="P22">
+        <v>403.2</v>
+      </c>
+      <c r="Q22">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="1">
+        <v>9900</v>
+      </c>
+      <c r="C23" s="1">
+        <v>896</v>
+      </c>
+      <c r="D23" s="1">
+        <v>13</v>
+      </c>
+      <c r="E23" s="1">
+        <v>3.9</v>
+      </c>
+      <c r="F23" s="1">
+        <v>646</v>
+      </c>
+      <c r="G23" s="1">
+        <v>108</v>
+      </c>
+      <c r="H23" s="1">
+        <v>720</v>
+      </c>
+      <c r="I23" s="1">
+        <v>166</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="K23" s="1">
+        <v>27.1</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0.19500000000000001</v>
+      </c>
+      <c r="M23" s="1">
+        <v>22.2</v>
+      </c>
+      <c r="N23" s="1">
+        <v>5870</v>
+      </c>
+      <c r="O23">
+        <v>6.7</v>
+      </c>
+      <c r="P23">
+        <v>306.60000000000002</v>
+      </c>
+      <c r="Q23">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="1">
+        <v>14100</v>
+      </c>
+      <c r="C24" s="1">
+        <v>968</v>
+      </c>
+      <c r="D24" s="1">
+        <v>14.8</v>
+      </c>
+      <c r="E24" s="1">
+        <v>3.86</v>
+      </c>
+      <c r="F24" s="1">
+        <v>796</v>
+      </c>
+      <c r="G24" s="1">
+        <v>113</v>
+      </c>
+      <c r="H24" s="1">
+        <v>896</v>
+      </c>
+      <c r="I24" s="1">
+        <v>174</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="K24" s="1">
+        <v>32.1</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="M24" s="1">
+        <v>23.8</v>
+      </c>
+      <c r="N24" s="1">
+        <v>6490.0000000000009</v>
+      </c>
+      <c r="O24">
+        <v>7.4</v>
+      </c>
+      <c r="P24">
+        <v>355</v>
+      </c>
+      <c r="Q24">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="1">
+        <v>21400</v>
+      </c>
+      <c r="C25" s="1">
+        <v>645</v>
+      </c>
+      <c r="D25" s="1">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="E25" s="1">
+        <v>3.11</v>
+      </c>
+      <c r="F25" s="1">
+        <v>950</v>
+      </c>
+      <c r="G25" s="1">
+        <v>84.6</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1100</v>
+      </c>
+      <c r="I25" s="1">
+        <v>133</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0.85899999999999999</v>
+      </c>
+      <c r="K25" s="1">
+        <v>43.8</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0.311</v>
+      </c>
+      <c r="M25" s="1">
+        <v>21.4</v>
+      </c>
+      <c r="N25" s="1">
+        <v>6659.9999999999991</v>
+      </c>
+      <c r="O25">
+        <v>7.6</v>
+      </c>
+      <c r="P25">
+        <v>449.8</v>
+      </c>
+      <c r="Q25">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="1">
+        <v>18300</v>
+      </c>
+      <c r="C26" s="1">
+        <v>635</v>
+      </c>
+      <c r="D26" s="1">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E26" s="1">
+        <v>3.06</v>
+      </c>
+      <c r="F26" s="1">
+        <v>899</v>
+      </c>
+      <c r="G26" s="1">
+        <v>88.6</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1030</v>
+      </c>
+      <c r="I26" s="1">
+        <v>139</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0.87</v>
+      </c>
+      <c r="K26" s="1">
+        <v>34.1</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0.246</v>
+      </c>
+      <c r="M26" s="1">
+        <v>29</v>
+      </c>
+      <c r="N26" s="1">
+        <v>6790.0000000000009</v>
+      </c>
+      <c r="O26">
+        <v>7.9</v>
+      </c>
+      <c r="P26">
+        <v>406.6</v>
+      </c>
+      <c r="Q26">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="1">
+        <v>11700</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1060</v>
+      </c>
+      <c r="D27" s="1">
+        <v>13</v>
+      </c>
+      <c r="E27" s="1">
+        <v>3.93</v>
+      </c>
+      <c r="F27" s="1">
+        <v>754</v>
+      </c>
+      <c r="G27" s="1">
+        <v>127</v>
+      </c>
+      <c r="H27" s="1">
+        <v>846</v>
+      </c>
+      <c r="I27" s="1">
+        <v>196</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="K27" s="1">
+        <v>23.6</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0.23400000000000001</v>
+      </c>
+      <c r="M27" s="1">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="N27" s="1">
+        <v>6880</v>
+      </c>
+      <c r="O27">
+        <v>7.9</v>
+      </c>
+      <c r="P27">
+        <v>310.39999999999998</v>
+      </c>
+      <c r="Q27">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="1">
+        <v>18700</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1020</v>
+      </c>
+      <c r="D28" s="1">
+        <v>16.5</v>
+      </c>
+      <c r="E28" s="1">
+        <v>3.85</v>
+      </c>
+      <c r="F28" s="1">
+        <v>930</v>
+      </c>
+      <c r="G28" s="1">
+        <v>115</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1050</v>
+      </c>
+      <c r="I28" s="1">
+        <v>178</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="K28" s="1">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="M28" s="1">
+        <v>23.1</v>
+      </c>
+      <c r="N28" s="1">
+        <v>6900</v>
+      </c>
+      <c r="O28">
+        <v>7.7</v>
+      </c>
+      <c r="P28">
+        <v>402.6</v>
+      </c>
+      <c r="Q28">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A29" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="1">
+        <v>16000</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1110</v>
+      </c>
+      <c r="D29" s="1">
+        <v>14.9</v>
+      </c>
+      <c r="E29" s="1">
+        <v>3.91</v>
+      </c>
+      <c r="F29" s="1">
+        <v>896</v>
+      </c>
+      <c r="G29" s="1">
+        <v>129</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1010</v>
+      </c>
+      <c r="I29" s="1">
+        <v>199</v>
+      </c>
+      <c r="J29" s="1">
+        <v>0.88200000000000001</v>
+      </c>
+      <c r="K29" s="1">
+        <v>28.8</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="M29" s="1">
+        <v>33.4</v>
+      </c>
+      <c r="N29" s="1">
+        <v>7259.9999999999991</v>
+      </c>
+      <c r="O29">
+        <v>8.1</v>
+      </c>
+      <c r="P29">
+        <v>358</v>
+      </c>
+      <c r="Q29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="1">
+        <v>25500</v>
+      </c>
+      <c r="C30" s="1">
+        <v>795</v>
+      </c>
+      <c r="D30" s="1">
+        <v>18.3</v>
+      </c>
+      <c r="E30" s="1">
+        <v>3.23</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1120</v>
+      </c>
+      <c r="G30" s="1">
+        <v>104</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1290</v>
+      </c>
+      <c r="I30" s="1">
+        <v>163</v>
+      </c>
+      <c r="J30" s="1">
+        <v>0.86799999999999999</v>
+      </c>
+      <c r="K30" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="M30" s="1">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="N30" s="1">
+        <v>7620</v>
+      </c>
+      <c r="O30">
+        <v>8.1</v>
+      </c>
+      <c r="P30">
+        <v>454.6</v>
+      </c>
+      <c r="Q30">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="1">
+        <v>21600</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1200</v>
+      </c>
+      <c r="D31" s="1">
+        <v>16.8</v>
+      </c>
+      <c r="E31" s="1">
+        <v>3.97</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1060</v>
+      </c>
+      <c r="G31" s="1">
+        <v>135</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1200</v>
+      </c>
+      <c r="I31" s="1">
+        <v>209</v>
+      </c>
+      <c r="J31" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="K31" s="1">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="M31" s="1">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="N31" s="1">
+        <v>7650</v>
+      </c>
+      <c r="O31">
+        <v>7.9</v>
+      </c>
+      <c r="P31">
+        <v>406.4</v>
+      </c>
+      <c r="Q31">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="1">
+        <v>35000</v>
+      </c>
+      <c r="C32" s="1">
+        <v>859</v>
+      </c>
+      <c r="D32" s="1">
+        <v>20.5</v>
+      </c>
+      <c r="E32" s="1">
+        <v>3.2</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1340</v>
+      </c>
+      <c r="G32" s="1">
+        <v>104</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1560</v>
+      </c>
+      <c r="I32" s="1">
+        <v>166</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0.84699999999999998</v>
+      </c>
+      <c r="K32" s="1">
+        <v>47</v>
+      </c>
+      <c r="L32" s="1">
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="M32" s="1">
+        <v>32</v>
+      </c>
+      <c r="N32" s="1">
+        <v>8370</v>
+      </c>
+      <c r="O32">
+        <v>8.9</v>
+      </c>
+      <c r="P32">
+        <v>524.70000000000005</v>
+      </c>
+      <c r="Q32">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="1">
+        <v>29400</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1450</v>
+      </c>
+      <c r="D33" s="1">
+        <v>18.5</v>
+      </c>
+      <c r="E33" s="1">
+        <v>4.12</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1300</v>
+      </c>
+      <c r="G33" s="1">
+        <v>153</v>
+      </c>
+      <c r="H33" s="1">
+        <v>1470</v>
+      </c>
+      <c r="I33" s="1">
+        <v>237</v>
+      </c>
+      <c r="J33" s="1">
+        <v>0.873</v>
+      </c>
+      <c r="K33" s="1">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="L33" s="1">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="M33" s="1">
+        <v>37.1</v>
+      </c>
+      <c r="N33" s="1">
+        <v>8550</v>
+      </c>
+      <c r="O33">
+        <v>8.5</v>
+      </c>
+      <c r="P33">
+        <v>453.4</v>
+      </c>
+      <c r="Q33">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="1">
+        <v>24300</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1360</v>
+      </c>
+      <c r="D34" s="1">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="E34" s="1">
+        <v>3.99</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1190</v>
+      </c>
+      <c r="G34" s="1">
+        <v>153</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1350</v>
+      </c>
+      <c r="I34" s="1">
+        <v>237</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="K34" s="1">
+        <v>30.4</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0.53300000000000003</v>
+      </c>
+      <c r="M34" s="1">
+        <v>46.1</v>
+      </c>
+      <c r="N34" s="1">
+        <v>8550</v>
+      </c>
+      <c r="O34">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="P34">
+        <v>409.4</v>
+      </c>
+      <c r="Q34">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A35" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="1">
+        <v>19500</v>
+      </c>
+      <c r="C35" s="1">
+        <v>1360</v>
+      </c>
+      <c r="D35" s="1">
+        <v>15.1</v>
+      </c>
+      <c r="E35" s="1">
+        <v>3.99</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1070</v>
+      </c>
+      <c r="G35" s="1">
+        <v>157</v>
+      </c>
+      <c r="H35" s="1">
+        <v>1210</v>
+      </c>
+      <c r="I35" s="1">
+        <v>243</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0.88600000000000001</v>
+      </c>
+      <c r="K35" s="1">
+        <v>24.4</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="M35" s="1">
+        <v>55.7</v>
+      </c>
+      <c r="N35" s="1">
+        <v>8550</v>
+      </c>
+      <c r="O35">
+        <v>9.1</v>
+      </c>
+      <c r="P35">
+        <v>363.4</v>
+      </c>
+      <c r="Q35">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="1">
+        <v>28900</v>
+      </c>
+      <c r="C36" s="1">
+        <v>913</v>
+      </c>
+      <c r="D36" s="1">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="E36" s="1">
+        <v>3.27</v>
+      </c>
+      <c r="F36" s="1">
+        <v>1260</v>
+      </c>
+      <c r="G36" s="1">
+        <v>119</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1450</v>
+      </c>
+      <c r="I36" s="1">
+        <v>187</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0.86799999999999999</v>
+      </c>
+      <c r="K36" s="1">
+        <v>33.6</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0.44800000000000001</v>
+      </c>
+      <c r="M36" s="1">
+        <v>47.7</v>
+      </c>
+      <c r="N36" s="1">
+        <v>8560</v>
+      </c>
+      <c r="O36">
+        <v>9</v>
+      </c>
+      <c r="P36">
+        <v>458</v>
+      </c>
+      <c r="Q36">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A37" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="1">
+        <v>32700</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1050</v>
+      </c>
+      <c r="D37" s="1">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="E37" s="1">
+        <v>3.33</v>
+      </c>
+      <c r="F37" s="1">
+        <v>1410</v>
+      </c>
+      <c r="G37" s="1">
+        <v>136</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1630</v>
+      </c>
+      <c r="I37" s="1">
+        <v>213</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0.872</v>
+      </c>
+      <c r="K37" s="1">
+        <v>30.1</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0.51800000000000002</v>
+      </c>
+      <c r="M37" s="1">
+        <v>65.900000000000006</v>
+      </c>
+      <c r="N37" s="1">
+        <v>9450</v>
+      </c>
+      <c r="O37">
+        <v>9.6</v>
+      </c>
+      <c r="P37">
+        <v>462</v>
+      </c>
+      <c r="Q37">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A38" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="1">
+        <v>27300</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1550</v>
+      </c>
+      <c r="D38" s="1">
+        <v>17</v>
+      </c>
+      <c r="E38" s="1">
+        <v>4.04</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1320</v>
+      </c>
+      <c r="G38" s="1">
+        <v>172</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1500</v>
+      </c>
+      <c r="I38" s="1">
+        <v>267</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0.88200000000000001</v>
+      </c>
+      <c r="K38" s="1">
+        <v>27.5</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="M38" s="1">
+        <v>62.8</v>
+      </c>
+      <c r="N38" s="1">
+        <v>9450</v>
+      </c>
+      <c r="O38">
+        <v>9.5</v>
+      </c>
+      <c r="P38">
+        <v>412.8</v>
+      </c>
+      <c r="Q38">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A39" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="1">
+        <v>33300</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1670</v>
+      </c>
+      <c r="D39" s="1">
+        <v>18.8</v>
+      </c>
+      <c r="E39" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1460</v>
+      </c>
+      <c r="G39" s="1">
+        <v>176</v>
+      </c>
+      <c r="H39" s="1">
+        <v>1650</v>
+      </c>
+      <c r="I39" s="1">
+        <v>272</v>
+      </c>
+      <c r="J39" s="1">
+        <v>0.877</v>
+      </c>
+      <c r="K39" s="1">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0.81799999999999995</v>
+      </c>
+      <c r="M39" s="1">
+        <v>51.8</v>
+      </c>
+      <c r="N39" s="1">
+        <v>9460</v>
+      </c>
+      <c r="O39">
+        <v>9</v>
+      </c>
+      <c r="P39">
+        <v>457</v>
+      </c>
+      <c r="Q39">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A40" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="1">
+        <v>41100</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1040</v>
+      </c>
+      <c r="D40" s="1">
+        <v>20.8</v>
+      </c>
+      <c r="E40" s="1">
+        <v>3.3</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1550</v>
+      </c>
+      <c r="G40" s="1">
+        <v>125</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1810</v>
+      </c>
+      <c r="I40" s="1">
+        <v>200</v>
+      </c>
+      <c r="J40" s="1">
+        <v>0.85299999999999998</v>
+      </c>
+      <c r="K40" s="1">
+        <v>41.1</v>
+      </c>
+      <c r="L40" s="1">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="M40" s="1">
+        <v>47.9</v>
+      </c>
+      <c r="N40" s="1">
+        <v>9520</v>
+      </c>
+      <c r="O40">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="P40">
+        <v>529.1</v>
+      </c>
+      <c r="Q40">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A41" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" s="1">
+        <v>37100</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1870</v>
+      </c>
+      <c r="D41" s="1">
+        <v>18.8</v>
+      </c>
+      <c r="E41" s="1">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1610</v>
+      </c>
+      <c r="G41" s="1">
+        <v>196</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1830</v>
+      </c>
+      <c r="I41" s="1">
+        <v>304</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0.879</v>
+      </c>
+      <c r="K41" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="L41" s="1">
+        <v>0.92200000000000004</v>
+      </c>
+      <c r="M41" s="1">
+        <v>69.2</v>
+      </c>
+      <c r="N41" s="1">
+        <v>10400</v>
+      </c>
+      <c r="O41">
+        <v>9.9</v>
+      </c>
+      <c r="P41">
+        <v>460</v>
+      </c>
+      <c r="Q41">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A42" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" s="1">
+        <v>47500</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2010</v>
+      </c>
+      <c r="D42" s="1">
+        <v>21.3</v>
+      </c>
+      <c r="E42" s="1">
+        <v>4.38</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1800</v>
+      </c>
+      <c r="G42" s="1">
+        <v>192</v>
+      </c>
+      <c r="H42" s="1">
+        <v>2060</v>
+      </c>
+      <c r="I42" s="1">
+        <v>300</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="K42" s="1">
+        <v>41.6</v>
+      </c>
+      <c r="L42" s="1">
+        <v>1.33</v>
+      </c>
+      <c r="M42" s="1">
+        <v>51.5</v>
+      </c>
+      <c r="N42" s="1">
+        <v>10500</v>
+      </c>
+      <c r="O42">
+        <v>9.6</v>
+      </c>
+      <c r="P42">
+        <v>528.29999999999995</v>
+      </c>
+      <c r="Q42">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="1">
+        <v>36600</v>
+      </c>
+      <c r="C43" s="1">
+        <v>1180</v>
+      </c>
+      <c r="D43" s="1">
+        <v>18.7</v>
+      </c>
+      <c r="E43" s="1">
+        <v>3.37</v>
+      </c>
+      <c r="F43" s="1">
+        <v>1570</v>
+      </c>
+      <c r="G43" s="1">
+        <v>153</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1810</v>
+      </c>
+      <c r="I43" s="1">
+        <v>240</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0.872</v>
+      </c>
+      <c r="K43" s="1">
+        <v>27.4</v>
+      </c>
+      <c r="L43" s="1">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="M43" s="1">
+        <v>89.2</v>
+      </c>
+      <c r="N43" s="1">
+        <v>10500</v>
+      </c>
+      <c r="O43">
+        <v>10.5</v>
+      </c>
+      <c r="P43">
+        <v>465.8</v>
+      </c>
+      <c r="Q43">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A44" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44" s="1">
+        <v>48500</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1270</v>
+      </c>
+      <c r="D44" s="1">
+        <v>21.2</v>
+      </c>
+      <c r="E44" s="1">
+        <v>3.44</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1820</v>
+      </c>
+      <c r="G44" s="1">
+        <v>153</v>
+      </c>
+      <c r="H44" s="1">
+        <v>2100</v>
+      </c>
+      <c r="I44" s="1">
+        <v>243</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="K44" s="1">
+        <v>35.5</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="M44" s="1">
+        <v>73.8</v>
+      </c>
+      <c r="N44" s="1">
+        <v>10800</v>
+      </c>
+      <c r="O44">
+        <v>10.3</v>
+      </c>
+      <c r="P44">
+        <v>534.9</v>
+      </c>
+      <c r="Q44">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A45" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="1">
+        <v>31700</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1830</v>
+      </c>
+      <c r="D45" s="1">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="E45" s="1">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1520</v>
+      </c>
+      <c r="G45" s="1">
+        <v>201</v>
+      </c>
+      <c r="H45" s="1">
+        <v>1730</v>
+      </c>
+      <c r="I45" s="1">
+        <v>313</v>
+      </c>
+      <c r="J45" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="K45" s="1">
+        <v>24.4</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0.72799999999999998</v>
+      </c>
+      <c r="M45" s="1">
+        <v>93</v>
+      </c>
+      <c r="N45" s="1">
+        <v>10900</v>
+      </c>
+      <c r="O45">
+        <v>10.9</v>
+      </c>
+      <c r="P45">
+        <v>417.2</v>
+      </c>
+      <c r="Q45">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A46" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" s="1">
+        <v>41000</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2090</v>
+      </c>
+      <c r="D46" s="1">
+        <v>19</v>
+      </c>
+      <c r="E46" s="1">
+        <v>4.29</v>
+      </c>
+      <c r="F46" s="1">
+        <v>1770</v>
+      </c>
+      <c r="G46" s="1">
+        <v>218</v>
+      </c>
+      <c r="H46" s="1">
+        <v>2010</v>
+      </c>
+      <c r="I46" s="1">
+        <v>338</v>
+      </c>
+      <c r="J46" s="1">
+        <v>0.878</v>
+      </c>
+      <c r="K46" s="1">
+        <v>28.3</v>
+      </c>
+      <c r="L46" s="1">
+        <v>1.04</v>
+      </c>
+      <c r="M46" s="1">
+        <v>90.7</v>
+      </c>
+      <c r="N46" s="1">
+        <v>11400</v>
+      </c>
+      <c r="O46">
+        <v>10.5</v>
+      </c>
+      <c r="P46">
+        <v>463.4</v>
+      </c>
+      <c r="Q46">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A47" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47" s="1">
+        <v>55200</v>
+      </c>
+      <c r="C47" s="1">
+        <v>2390</v>
+      </c>
+      <c r="D47" s="1">
+        <v>21.7</v>
+      </c>
+      <c r="E47" s="1">
+        <v>4.51</v>
+      </c>
+      <c r="F47" s="1">
+        <v>2070</v>
+      </c>
+      <c r="G47" s="1">
+        <v>228</v>
+      </c>
+      <c r="H47" s="1">
+        <v>2360</v>
+      </c>
+      <c r="I47" s="1">
+        <v>355</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0.873</v>
+      </c>
+      <c r="K47" s="1">
+        <v>36.4</v>
+      </c>
+      <c r="L47" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="M47" s="1">
+        <v>75.7</v>
+      </c>
+      <c r="N47" s="1">
+        <v>11700</v>
+      </c>
+      <c r="O47">
+        <v>10.1</v>
+      </c>
+      <c r="P47">
+        <v>533.1</v>
+      </c>
+      <c r="Q47">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A48" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B48" s="1">
+        <v>45700</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2350</v>
+      </c>
+      <c r="D48" s="1">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="E48" s="1">
+        <v>4.33</v>
+      </c>
+      <c r="F48" s="1">
+        <v>1960</v>
+      </c>
+      <c r="G48" s="1">
+        <v>243</v>
+      </c>
+      <c r="H48" s="1">
+        <v>2230</v>
+      </c>
+      <c r="I48" s="1">
+        <v>379</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="K48" s="1">
+        <v>25.8</v>
+      </c>
+      <c r="L48" s="1">
+        <v>1.18</v>
+      </c>
+      <c r="M48" s="1">
+        <v>121</v>
+      </c>
+      <c r="N48" s="1">
+        <v>12500</v>
+      </c>
+      <c r="O48">
+        <v>11.4</v>
+      </c>
+      <c r="P48">
+        <v>467.2</v>
+      </c>
+      <c r="Q48">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A49" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" s="1">
+        <v>61500</v>
+      </c>
+      <c r="C49" s="1">
+        <v>2690</v>
+      </c>
+      <c r="D49" s="1">
+        <v>21.9</v>
+      </c>
+      <c r="E49" s="1">
+        <v>4.57</v>
+      </c>
+      <c r="F49" s="1">
+        <v>2290</v>
+      </c>
+      <c r="G49" s="1">
+        <v>256</v>
+      </c>
+      <c r="H49" s="1">
+        <v>2610</v>
+      </c>
+      <c r="I49" s="1">
+        <v>399</v>
+      </c>
+      <c r="J49" s="1">
+        <v>0.874</v>
+      </c>
+      <c r="K49" s="1">
+        <v>33.1</v>
+      </c>
+      <c r="L49" s="1">
+        <v>1.81</v>
+      </c>
+      <c r="M49" s="1">
+        <v>101</v>
+      </c>
+      <c r="N49" s="1">
+        <v>12900</v>
+      </c>
+      <c r="O49">
+        <v>10.8</v>
+      </c>
+      <c r="P49">
+        <v>536.70000000000005</v>
+      </c>
+      <c r="Q49">
+        <v>17.399999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A50" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50" s="1">
+        <v>48900</v>
+      </c>
+      <c r="C50" s="1">
+        <v>2510</v>
+      </c>
+      <c r="D50" s="1">
+        <v>19</v>
+      </c>
+      <c r="E50" s="1">
+        <v>4.32</v>
+      </c>
+      <c r="F50" s="1">
+        <v>2080</v>
+      </c>
+      <c r="G50" s="1">
+        <v>259</v>
+      </c>
+      <c r="H50" s="1">
+        <v>2390</v>
+      </c>
+      <c r="I50" s="1">
+        <v>405</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0.876</v>
+      </c>
+      <c r="K50" s="1">
+        <v>24.4</v>
+      </c>
+      <c r="L50" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="M50" s="1">
+        <v>146</v>
+      </c>
+      <c r="N50" s="1">
+        <v>13500</v>
+      </c>
+      <c r="O50">
+        <v>12.6</v>
+      </c>
+      <c r="P50">
+        <v>469.2</v>
+      </c>
+      <c r="Q50">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A51" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B51" s="1">
+        <v>66800</v>
+      </c>
+      <c r="C51" s="1">
+        <v>2940</v>
+      </c>
+      <c r="D51" s="1">
+        <v>21.9</v>
+      </c>
+      <c r="E51" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F51" s="1">
+        <v>2480</v>
+      </c>
+      <c r="G51" s="1">
+        <v>279</v>
+      </c>
+      <c r="H51" s="1">
+        <v>2830</v>
+      </c>
+      <c r="I51" s="1">
+        <v>436</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0.875</v>
+      </c>
+      <c r="K51" s="1">
+        <v>30.9</v>
+      </c>
+      <c r="L51" s="1">
+        <v>1.99</v>
+      </c>
+      <c r="M51" s="1">
+        <v>126</v>
+      </c>
+      <c r="N51" s="1">
+        <v>13900</v>
+      </c>
+      <c r="O51">
+        <v>11.6</v>
+      </c>
+      <c r="P51">
+        <v>539.5</v>
+      </c>
+      <c r="Q51">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A52" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B52" s="1">
+        <v>76000</v>
+      </c>
+      <c r="C52" s="1">
+        <v>3390</v>
+      </c>
+      <c r="D52" s="1">
+        <v>22.1</v>
+      </c>
+      <c r="E52" s="1">
+        <v>4.67</v>
+      </c>
+      <c r="F52" s="1">
+        <v>2790</v>
+      </c>
+      <c r="G52" s="1">
+        <v>320</v>
+      </c>
+      <c r="H52" s="1">
+        <v>3200</v>
+      </c>
+      <c r="I52" s="1">
+        <v>500</v>
+      </c>
+      <c r="J52" s="1">
+        <v>0.878</v>
+      </c>
+      <c r="K52" s="1">
+        <v>27.6</v>
+      </c>
+      <c r="L52" s="1">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="M52" s="1">
+        <v>178</v>
+      </c>
+      <c r="N52" s="1">
+        <v>15500</v>
+      </c>
+      <c r="O52">
+        <v>12.7</v>
+      </c>
+      <c r="P52">
+        <v>544.5</v>
+      </c>
+      <c r="Q52">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A53" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" s="1">
+        <v>63800</v>
+      </c>
+      <c r="C53" s="1">
+        <v>3350</v>
+      </c>
+      <c r="D53" s="1">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="E53" s="1">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="F53" s="1">
+        <v>2660</v>
+      </c>
+      <c r="G53" s="1">
+        <v>341</v>
+      </c>
+      <c r="H53" s="1">
+        <v>3070</v>
+      </c>
+      <c r="I53" s="1">
+        <v>535</v>
+      </c>
+      <c r="J53" s="1">
+        <v>0.879</v>
+      </c>
+      <c r="K53" s="1">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="L53" s="1">
+        <v>1.73</v>
+      </c>
+      <c r="M53" s="1">
+        <v>292</v>
+      </c>
+      <c r="N53" s="1">
+        <v>17000</v>
+      </c>
+      <c r="O53">
+        <v>15.3</v>
+      </c>
+      <c r="P53">
+        <v>480.6</v>
+      </c>
+      <c r="Q53">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A54" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B54" s="1">
+        <v>86100</v>
+      </c>
+      <c r="C54" s="1">
+        <v>3860</v>
+      </c>
+      <c r="D54" s="1">
+        <v>22.1</v>
+      </c>
+      <c r="E54" s="1">
+        <v>4.68</v>
+      </c>
+      <c r="F54" s="1">
+        <v>3140</v>
+      </c>
+      <c r="G54" s="1">
+        <v>361</v>
+      </c>
+      <c r="H54" s="1">
+        <v>3610</v>
+      </c>
+      <c r="I54" s="1">
+        <v>568</v>
+      </c>
+      <c r="J54" s="1">
+        <v>0.874</v>
+      </c>
+      <c r="K54" s="1">
+        <v>24.9</v>
+      </c>
+      <c r="L54" s="1">
+        <v>2.67</v>
+      </c>
+      <c r="M54" s="1">
+        <v>250</v>
+      </c>
+      <c r="N54" s="1">
+        <v>17600</v>
+      </c>
+      <c r="O54">
+        <v>14.7</v>
+      </c>
+      <c r="P54">
+        <v>549.1</v>
+      </c>
+      <c r="Q54">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="A55" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B55" s="1">
+        <v>79800</v>
+      </c>
+      <c r="C55" s="1">
+        <v>4250</v>
+      </c>
+      <c r="D55" s="1">
+        <v>19.7</v>
+      </c>
+      <c r="E55" s="1">
+        <v>4.55</v>
+      </c>
+      <c r="F55" s="1">
+        <v>3240</v>
+      </c>
+      <c r="G55" s="1">
+        <v>426</v>
+      </c>
+      <c r="H55" s="1">
+        <v>3780</v>
+      </c>
+      <c r="I55" s="1">
+        <v>672</v>
+      </c>
+      <c r="J55" s="1">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="K55" s="1">
+        <v>16.5</v>
+      </c>
+      <c r="L55" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="M55" s="1">
+        <v>515</v>
+      </c>
+      <c r="N55" s="1">
+        <v>20600</v>
+      </c>
+      <c r="O55">
+        <v>18</v>
+      </c>
+      <c r="P55">
+        <v>492</v>
+      </c>
+      <c r="Q55">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/UB-2.xlsx
+++ b/UB-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/twalha/Documents/GitHub/g6-analysis-tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E03722-B37D-5A4C-9A81-A6F032BD8E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A92AA4-4F38-2E45-9BDF-B9203209AFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Steel Section Properties Data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t>Section Designation</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t>457x191x161 +</t>
+  </si>
+  <si>
+    <t>b (mm)</t>
   </si>
 </sst>
 </file>
@@ -519,10 +522,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:R55"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -577,8 +580,11 @@
       <c r="R1" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+      <c r="S1" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -621,8 +627,11 @@
       <c r="R2" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+      <c r="S2" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -665,8 +674,11 @@
       <c r="R3" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+      <c r="S3" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -709,8 +721,11 @@
       <c r="R4" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+      <c r="S4" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
@@ -753,8 +768,11 @@
       <c r="R5" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+      <c r="S5" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -797,8 +815,11 @@
       <c r="R6" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+      <c r="S6" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -841,8 +862,11 @@
       <c r="R7" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+      <c r="S7" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -885,8 +909,11 @@
       <c r="R8" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+      <c r="S8" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -929,8 +956,11 @@
       <c r="R9" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+      <c r="S9" s="2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
@@ -973,8 +1003,11 @@
       <c r="R10" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+      <c r="S10" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -1017,8 +1050,11 @@
       <c r="R11" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+      <c r="S11" s="2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>27</v>
       </c>
@@ -1061,8 +1097,11 @@
       <c r="R12" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+      <c r="S12" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
@@ -1105,8 +1144,11 @@
       <c r="R13" s="2">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+      <c r="S13" s="2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>29</v>
       </c>
@@ -1149,8 +1191,11 @@
       <c r="R14" s="2">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+      <c r="S14" s="2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>30</v>
       </c>
@@ -1193,8 +1238,11 @@
       <c r="R15" s="2">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" ht="13" x14ac:dyDescent="0.15">
+      <c r="S15" s="2">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>31</v>
       </c>
@@ -1237,8 +1285,11 @@
       <c r="R16" s="2">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S16" s="2">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -1290,8 +1341,11 @@
       <c r="Q17">
         <v>8.5</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S17">
+        <v>125.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -1343,8 +1397,11 @@
       <c r="Q18">
         <v>8.6</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S18">
+        <v>141.80000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>35</v>
       </c>
@@ -1396,8 +1453,11 @@
       <c r="Q19">
         <v>10.7</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S19">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>36</v>
       </c>
@@ -1449,8 +1509,11 @@
       <c r="Q20">
         <v>10.199999999999999</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S20">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
         <v>37</v>
       </c>
@@ -1502,8 +1565,11 @@
       <c r="Q21">
         <v>9.6999999999999993</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S21">
+        <v>171.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>38</v>
       </c>
@@ -1555,8 +1621,11 @@
       <c r="Q22">
         <v>11.2</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S22">
+        <v>142.19999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>39</v>
       </c>
@@ -1608,8 +1677,11 @@
       <c r="Q23">
         <v>11.8</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S23">
+        <v>165.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
         <v>40</v>
       </c>
@@ -1661,8 +1733,11 @@
       <c r="Q24">
         <v>11.5</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S24">
+        <v>171.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>41</v>
       </c>
@@ -1714,8 +1789,11 @@
       <c r="Q25">
         <v>10.9</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S25">
+        <v>152.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
         <v>42</v>
       </c>
@@ -1767,8 +1845,11 @@
       <c r="Q26">
         <v>12.9</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S26">
+        <v>143.30000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
         <v>43</v>
       </c>
@@ -1820,8 +1901,11 @@
       <c r="Q27">
         <v>13.7</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S27">
+        <v>166.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
         <v>44</v>
       </c>
@@ -1873,8 +1957,11 @@
       <c r="Q28">
         <v>10.9</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S28">
+        <v>177.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
         <v>45</v>
       </c>
@@ -1926,8 +2013,11 @@
       <c r="Q29">
         <v>13</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S29">
+        <v>172.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
         <v>46</v>
       </c>
@@ -1979,8 +2069,11 @@
       <c r="Q30">
         <v>13.3</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S30">
+        <v>152.9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
         <v>47</v>
       </c>
@@ -2032,8 +2125,11 @@
       <c r="Q31">
         <v>12.8</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S31">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -2085,8 +2181,11 @@
       <c r="Q32">
         <v>11.4</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S32">
+        <v>165.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
         <v>49</v>
       </c>
@@ -2138,8 +2237,11 @@
       <c r="Q33">
         <v>12.7</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S33">
+        <v>189.9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
         <v>50</v>
       </c>
@@ -2191,8 +2293,11 @@
       <c r="Q34">
         <v>14.3</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S34">
+        <v>178.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
         <v>51</v>
       </c>
@@ -2244,8 +2349,11 @@
       <c r="Q35">
         <v>15.7</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S35">
+        <v>173.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
         <v>52</v>
       </c>
@@ -2297,8 +2405,11 @@
       <c r="Q36">
         <v>15</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S36">
+        <v>153.80000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
         <v>53</v>
       </c>
@@ -2350,8 +2461,11 @@
       <c r="Q37">
         <v>17</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S37">
+        <v>154.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
         <v>54</v>
       </c>
@@ -2403,8 +2517,11 @@
       <c r="Q38">
         <v>16</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S38">
+        <v>179.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
         <v>55</v>
       </c>
@@ -2456,8 +2573,11 @@
       <c r="Q39">
         <v>14.5</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S39">
+        <v>190.4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
         <v>56</v>
       </c>
@@ -2509,8 +2629,11 @@
       <c r="Q40">
         <v>13.6</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S40">
+        <v>165.9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
         <v>57</v>
       </c>
@@ -2562,8 +2685,11 @@
       <c r="Q41">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S41">
+        <v>191.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
         <v>58</v>
       </c>
@@ -2615,8 +2741,11 @@
       <c r="Q42">
         <v>13.2</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S42">
+        <v>208.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
         <v>59</v>
       </c>
@@ -2668,8 +2797,11 @@
       <c r="Q43">
         <v>18.899999999999999</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S43">
+        <v>155.30000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>60</v>
       </c>
@@ -2721,8 +2853,11 @@
       <c r="Q44">
         <v>16.5</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S44">
+        <v>166.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
         <v>61</v>
       </c>
@@ -2774,8 +2909,11 @@
       <c r="Q45">
         <v>18.2</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S45">
+        <v>181.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>62</v>
       </c>
@@ -2827,8 +2965,11 @@
       <c r="Q46">
         <v>17.7</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S46">
+        <v>191.9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
         <v>63</v>
       </c>
@@ -2880,8 +3021,11 @@
       <c r="Q47">
         <v>15.6</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S47">
+        <v>209.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
         <v>64</v>
       </c>
@@ -2933,8 +3077,11 @@
       <c r="Q48">
         <v>19.600000000000001</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S48">
+        <v>192.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
         <v>65</v>
       </c>
@@ -2986,8 +3133,11 @@
       <c r="Q49">
         <v>17.399999999999999</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S49">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
         <v>66</v>
       </c>
@@ -3039,8 +3189,11 @@
       <c r="Q50">
         <v>20.6</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S50">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
         <v>67</v>
       </c>
@@ -3092,8 +3245,11 @@
       <c r="Q51">
         <v>18.8</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S51">
+        <v>210.8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
         <v>68</v>
       </c>
@@ -3145,8 +3301,11 @@
       <c r="Q52">
         <v>21.3</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S52">
+        <v>211.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
         <v>69</v>
       </c>
@@ -3198,8 +3357,11 @@
       <c r="Q53">
         <v>26.3</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S53">
+        <v>196.7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
         <v>70</v>
       </c>
@@ -3251,8 +3413,11 @@
       <c r="Q54">
         <v>23.6</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" ht="13" x14ac:dyDescent="0.15">
+      <c r="S54">
+        <v>213.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="13" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
         <v>71</v>
       </c>
@@ -3303,6 +3468,9 @@
       </c>
       <c r="Q55">
         <v>32</v>
+      </c>
+      <c r="S55">
+        <v>199.4</v>
       </c>
     </row>
   </sheetData>

--- a/UB-2.xlsx
+++ b/UB-2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A92AA4-4F38-2E45-9BDF-B9203209AFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Steel Section Properties Data" sheetId="1" r:id="rId1"/>

--- a/UB-2.xlsx
+++ b/UB-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/twalha/Documents/GitHub/g6-analysis-tool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A92AA4-4F38-2E45-9BDF-B9203209AFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0B165A-5DAB-3449-B2BA-1229AC16E705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Steel Section Properties Data" sheetId="1" r:id="rId1"/>
@@ -600,8 +600,12 @@
       <c r="E2" s="2">
         <v>1.05</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
+      <c r="F2" s="1">
+        <v>17.570175438596493</v>
+      </c>
+      <c r="G2" s="1">
+        <v>2.3653846153846154</v>
+      </c>
       <c r="H2" s="2">
         <v>20.03</v>
       </c>
@@ -647,8 +651,12 @@
       <c r="E3" s="2">
         <v>1.24</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="F3" s="1">
+        <v>30</v>
+      </c>
+      <c r="G3" s="1">
+        <v>3.7115384615384612</v>
+      </c>
       <c r="H3" s="2">
         <v>34.200000000000003</v>
       </c>
@@ -694,8 +702,12 @@
       <c r="E4" s="2">
         <v>1.45</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
+      <c r="F4" s="1">
+        <v>46.456140350877199</v>
+      </c>
+      <c r="G4" s="1">
+        <v>5.5448717948717947</v>
+      </c>
       <c r="H4" s="2">
         <v>52.96</v>
       </c>
@@ -741,8 +753,12 @@
       <c r="E5" s="2">
         <v>1.65</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
+      <c r="F5" s="1">
+        <v>67.824561403508767</v>
+      </c>
+      <c r="G5" s="1">
+        <v>7.8910256410256414</v>
+      </c>
       <c r="H5" s="2">
         <v>77.319999999999993</v>
       </c>
@@ -788,8 +804,12 @@
       <c r="E6" s="2">
         <v>1.84</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="F6" s="1">
+        <v>95.350877192982466</v>
+      </c>
+      <c r="G6" s="1">
+        <v>10.679487179487179</v>
+      </c>
       <c r="H6" s="2">
         <v>108.7</v>
       </c>
@@ -835,8 +855,12 @@
       <c r="E7" s="2">
         <v>2.0499999999999998</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="F7" s="1">
+        <v>128.33333333333334</v>
+      </c>
+      <c r="G7" s="1">
+        <v>14.205128205128204</v>
+      </c>
       <c r="H7" s="2">
         <v>146.30000000000001</v>
       </c>
@@ -882,8 +906,12 @@
       <c r="E8" s="2">
         <v>2.2400000000000002</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="F8" s="1">
+        <v>170.43859649122808</v>
+      </c>
+      <c r="G8" s="1">
+        <v>18.25</v>
+      </c>
       <c r="H8" s="2">
         <v>194.3</v>
       </c>
@@ -929,8 +957,12 @@
       <c r="E9" s="2">
         <v>2.48</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+      <c r="F9" s="1">
+        <v>221.0526315789474</v>
+      </c>
+      <c r="G9" s="1">
+        <v>23.878205128205128</v>
+      </c>
       <c r="H9" s="2">
         <v>252</v>
       </c>
@@ -976,8 +1008,12 @@
       <c r="E10" s="2">
         <v>2.69</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="F10" s="1">
+        <v>284.47368421052636</v>
+      </c>
+      <c r="G10" s="1">
+        <v>30.301282051282051</v>
+      </c>
       <c r="H10" s="2">
         <v>324.3</v>
       </c>
@@ -1023,8 +1059,12 @@
       <c r="E11" s="2">
         <v>3.02</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
+      <c r="F11" s="1">
+        <v>376.22807017543863</v>
+      </c>
+      <c r="G11" s="1">
+        <v>39.871794871794876</v>
+      </c>
       <c r="H11" s="2">
         <v>428.9</v>
       </c>
@@ -1070,8 +1110,12 @@
       <c r="E12" s="2">
         <v>3.35</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
+      <c r="F12" s="1">
+        <v>488.68421052631584</v>
+      </c>
+      <c r="G12" s="1">
+        <v>51.602564102564102</v>
+      </c>
       <c r="H12" s="2">
         <v>557.1</v>
       </c>
@@ -1117,8 +1161,12 @@
       <c r="E13" s="2">
         <v>3.55</v>
       </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
+      <c r="F13" s="1">
+        <v>625.52631578947376</v>
+      </c>
+      <c r="G13" s="1">
+        <v>63.153846153846146</v>
+      </c>
       <c r="H13" s="2">
         <v>713.1</v>
       </c>
@@ -1164,8 +1212,12 @@
       <c r="E14" s="2">
         <v>3.79</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
+      <c r="F14" s="1">
+        <v>792.63157894736855</v>
+      </c>
+      <c r="G14" s="1">
+        <v>78.717948717948715</v>
+      </c>
       <c r="H14" s="2">
         <v>903.6</v>
       </c>
@@ -1211,8 +1263,12 @@
       <c r="E15" s="2">
         <v>3.95</v>
       </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
+      <c r="F15" s="1">
+        <v>1014.0350877192983</v>
+      </c>
+      <c r="G15" s="1">
+        <v>93.84615384615384</v>
+      </c>
       <c r="H15" s="2">
         <v>1156</v>
       </c>
@@ -1258,8 +1314,12 @@
       <c r="E16" s="2">
         <v>4.12</v>
       </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+      <c r="F16" s="1">
+        <v>1315.7894736842106</v>
+      </c>
+      <c r="G16" s="1">
+        <v>113.07692307692308</v>
+      </c>
       <c r="H16" s="2">
         <v>1500</v>
       </c>
